--- a/artfynd/S 781-2024 artfynd.xlsx
+++ b/artfynd/S 781-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,64 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1849499</v>
+        <v>135207762</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>99112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högåsabergen, bäck norr om, Sm</t>
+          <t>Högåsabergen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433755</v>
+        <v>433704</v>
       </c>
       <c r="R2" t="n">
-        <v>6378877</v>
+        <v>6379461</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +756,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-04-05</t>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-04-05</t>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,76 +780,76 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Blandsumpskog vid bäck</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Björk, gran</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Hans Boberg, Håkan  Åberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74579220</v>
+        <v>1849499</v>
       </c>
       <c r="B3" t="n">
-        <v>99140</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>L28 Högåsabergen nord, Sm</t>
+          <t>Högåsabergen, bäck norr om, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433982</v>
+        <v>433755</v>
       </c>
       <c r="R3" t="n">
-        <v>6378958</v>
+        <v>6378877</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,17 +873,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>2011-04-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6D6h 1907. SOM: Listera cordata. LEG: Lennart Stenberg, Lennart Persson</t>
+          <t>2011-04-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,82 +892,71 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Sluttande skog i vitmossa</t>
+          <t>Blandsumpskog vid bäck</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Björk, gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106357869</v>
+        <v>74579220</v>
       </c>
       <c r="B4" t="n">
-        <v>57864</v>
+        <v>99140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100011</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bongebo skogsbilväg b, Sm</t>
+          <t>L28 Högåsabergen nord, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438337</v>
+        <v>433982</v>
       </c>
       <c r="R4" t="n">
-        <v>6378990</v>
+        <v>6378958</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,27 +980,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>1987-12-31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flög fram och tillbala bland trädtopparna. Ungfågel.</t>
+          <t>Smålands flora 2007: KOO: 6D6h 1907. SOM: Listera cordata. LEG: Lennart Stenberg, Lennart Persson</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,76 +1001,85 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Sluttande skog i vitmossa</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marcus Svensson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marcus Svensson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103123401</v>
+        <v>106357869</v>
       </c>
       <c r="B5" t="n">
-        <v>57141</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100011</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bongebo skogsbilväg a, Sm</t>
+          <t>Bongebo skogsbilväg b, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438605</v>
+        <v>438337</v>
       </c>
       <c r="R5" t="n">
-        <v>6378918</v>
+        <v>6378990</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,12 +1103,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2023-01-31</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2023-01-31</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flög fram och tillbala bland trädtopparna. Ungfågel.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,57 +1150,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1849514</v>
+        <v>103123401</v>
       </c>
       <c r="B6" t="n">
-        <v>79327</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svansjön, sydväst om, Sm</t>
+          <t>Bongebo skogsbilväg a, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435286</v>
+        <v>438605</v>
       </c>
       <c r="R6" t="n">
-        <v>6378953</v>
+        <v>6378918</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,12 +1227,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2011-04-20</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2011-04-20</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,63 +1243,53 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Marcus Svensson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Marcus Svensson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1906155</v>
+        <v>1849514</v>
       </c>
       <c r="B7" t="n">
-        <v>80367</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1291,14 +1299,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ödetomt, norr om Gräsö mosse, Sm</t>
+          <t>Svansjön, sydväst om, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437466</v>
+        <v>435286</v>
       </c>
       <c r="R7" t="n">
-        <v>6377842</v>
+        <v>6378953</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,12 +1352,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Ödetomt</t>
+          <t>Tallmosse</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Lönn, vårdträd och högstubbe</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1367,32 +1375,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6703384</v>
+        <v>1906155</v>
       </c>
       <c r="B8" t="n">
-        <v>80477</v>
+        <v>80367</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229504</v>
+        <v>6457</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1483,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1937538</v>
+        <v>6703384</v>
       </c>
       <c r="B9" t="n">
-        <v>75428</v>
+        <v>80477</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,26 +1502,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>229504</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1523,14 +1531,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gäddegöl, nordöst om, Sm</t>
+          <t>Ödetomt, norr om Gräsö mosse, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436083</v>
+        <v>437466</v>
       </c>
       <c r="R9" t="n">
-        <v>6378073</v>
+        <v>6377842</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,12 +1584,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Ödetomt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Lönn, vårdträd och högstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1599,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>74965281</v>
+        <v>1937538</v>
       </c>
       <c r="B10" t="n">
-        <v>110077</v>
+        <v>75428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,37 +1618,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>L1 Punkt 320.0 500 m VNV, Sm</t>
+          <t>Gäddegöl, nordöst om, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435808</v>
+        <v>436083</v>
       </c>
       <c r="R10" t="n">
-        <v>6376681</v>
+        <v>6378073</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1664,17 +1681,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1985-01-01</t>
+          <t>2011-04-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6D5h 4625. SOM: Scorzonera humilis. LEG: Lennart Stenberg, Lennart Persson</t>
+          <t>2011-04-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,70 +1700,71 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>200849</v>
+        <v>74965281</v>
       </c>
       <c r="B11" t="n">
-        <v>96705</v>
+        <v>110077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>535</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brännegölen, norr om, Sm</t>
+          <t>L1 Punkt 320.0 500 m VNV, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434522</v>
+        <v>435808</v>
       </c>
       <c r="R11" t="n">
-        <v>6377835</v>
+        <v>6376681</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1775,12 +1788,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2011-04-05</t>
+          <t>1985-01-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2011-04-05</t>
+          <t>1989-12-31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6D5h 4625. SOM: Scorzonera humilis. LEG: Lennart Stenberg, Lennart Persson</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,33 +1812,32 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Bergbrant vid sumpskog</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Klippa</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>817729</v>
+        <v>200849</v>
       </c>
       <c r="B12" t="n">
-        <v>97733</v>
+        <v>96705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1828,21 +1845,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>535</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1924,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1276843</v>
+        <v>817729</v>
       </c>
       <c r="B13" t="n">
-        <v>91893</v>
+        <v>97733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,43 +1952,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4660</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Högåsabergen, Sm</t>
+          <t>Brännegölen, norr om, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433902</v>
+        <v>434522</v>
       </c>
       <c r="R13" t="n">
-        <v>6378202</v>
+        <v>6377835</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,12 +2025,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Bergbrant</t>
+          <t>Bergbrant vid sumpskog</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Asp, grov högstubbe</t>
+          <t>Klippa</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2040,32 +2048,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1849500</v>
+        <v>1276843</v>
       </c>
       <c r="B14" t="n">
-        <v>79327</v>
+        <v>91893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4660</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2080,17 +2088,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fågelåsen, Sm</t>
+          <t>Högåsabergen, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434561</v>
+        <v>433902</v>
       </c>
       <c r="R14" t="n">
-        <v>6376516</v>
+        <v>6378202</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2138,7 +2146,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Asp, grov högstubbe</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2156,37 +2164,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1937533</v>
+        <v>1849500</v>
       </c>
       <c r="B15" t="n">
-        <v>75428</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2196,17 +2204,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Brännegölen, norr om, Sm</t>
+          <t>Fågelåsen, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434600</v>
+        <v>434561</v>
       </c>
       <c r="R15" t="n">
-        <v>6377978</v>
+        <v>6376516</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2249,12 +2257,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Bergbrant</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Gran, senvuxen</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2272,56 +2280,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>66535341</v>
+        <v>1937533</v>
       </c>
       <c r="B16" t="n">
-        <v>57141</v>
+        <v>75428</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bondö, Sm</t>
+          <t>Brännegölen, norr om, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437829</v>
+        <v>434600</v>
       </c>
       <c r="R16" t="n">
-        <v>6376541</v>
+        <v>6377978</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2348,22 +2354,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:36</t>
+          <t>2011-04-05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:36</t>
+          <t>2011-04-05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,19 +2370,147 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Gran, senvuxen</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>66535341</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bondö, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>437829</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6376541</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vaggeryd</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bondstorp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2017-07-03</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2017-07-03</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 781-2024 artfynd.xlsx
+++ b/artfynd/S 781-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135207762</v>
+        <v>135472902</v>
       </c>
       <c r="B2" t="n">
-        <v>99112</v>
+        <v>58061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,53 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>102626</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högåsabergen, Sm</t>
+          <t>Tranflyet, Tranflyet, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433704</v>
+        <v>437072</v>
       </c>
       <c r="R2" t="n">
-        <v>6379461</v>
+        <v>6379592</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,76 +773,82 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Boberg</t>
+          <t>Bob Lind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Boberg, Håkan  Åberg</t>
+          <t>Bob Lind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1849499</v>
+        <v>135207762</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>99112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högåsabergen, bäck norr om, Sm</t>
+          <t>Högåsabergen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433755</v>
+        <v>433704</v>
       </c>
       <c r="R3" t="n">
-        <v>6378877</v>
+        <v>6379461</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,12 +872,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-04-05</t>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-04-05</t>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,76 +896,76 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Blandsumpskog vid bäck</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Björk, gran</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Hans Boberg, Håkan  Åberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74579220</v>
+        <v>1849499</v>
       </c>
       <c r="B4" t="n">
-        <v>99140</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>L28 Högåsabergen nord, Sm</t>
+          <t>Högåsabergen, bäck norr om, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433982</v>
+        <v>433755</v>
       </c>
       <c r="R4" t="n">
-        <v>6378958</v>
+        <v>6378877</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,17 +989,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>2011-04-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6D6h 1907. SOM: Listera cordata. LEG: Lennart Stenberg, Lennart Persson</t>
+          <t>2011-04-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,82 +1008,71 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Sluttande skog i vitmossa</t>
+          <t>Blandsumpskog vid bäck</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Björk, gran</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106357869</v>
+        <v>74579220</v>
       </c>
       <c r="B5" t="n">
-        <v>57864</v>
+        <v>99140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100011</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bongebo skogsbilväg b, Sm</t>
+          <t>L28 Högåsabergen nord, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438337</v>
+        <v>433982</v>
       </c>
       <c r="R5" t="n">
-        <v>6378990</v>
+        <v>6378958</v>
       </c>
       <c r="S5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,27 +1096,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>1987-12-31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flög fram och tillbala bland trädtopparna. Ungfågel.</t>
+          <t>Smålands flora 2007: KOO: 6D6h 1907. SOM: Listera cordata. LEG: Lennart Stenberg, Lennart Persson</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,76 +1117,85 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Sluttande skog i vitmossa</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marcus Svensson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marcus Svensson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103123401</v>
+        <v>106357869</v>
       </c>
       <c r="B6" t="n">
-        <v>57141</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100011</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bongebo skogsbilväg a, Sm</t>
+          <t>Bongebo skogsbilväg b, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438605</v>
+        <v>438337</v>
       </c>
       <c r="R6" t="n">
-        <v>6378918</v>
+        <v>6378990</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,12 +1219,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2023-01-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>2023-01-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flög fram och tillbala bland trädtopparna. Ungfågel.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,57 +1266,60 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1849514</v>
+        <v>103123401</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svansjön, sydväst om, Sm</t>
+          <t>Bongebo skogsbilväg a, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435286</v>
+        <v>438605</v>
       </c>
       <c r="R7" t="n">
-        <v>6378953</v>
+        <v>6378918</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,12 +1343,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2011-04-20</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2011-04-20</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,63 +1359,53 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Marcus Svensson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Marcus Svensson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1906155</v>
+        <v>1849514</v>
       </c>
       <c r="B8" t="n">
-        <v>80367</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1415,14 +1415,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ödetomt, norr om Gräsö mosse, Sm</t>
+          <t>Svansjön, sydväst om, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437466</v>
+        <v>435286</v>
       </c>
       <c r="R8" t="n">
-        <v>6377842</v>
+        <v>6378953</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Ödetomt</t>
+          <t>Tallmosse</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Lönn, vårdträd och högstubbe</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1491,32 +1491,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6703384</v>
+        <v>1906155</v>
       </c>
       <c r="B9" t="n">
-        <v>80477</v>
+        <v>80367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229504</v>
+        <v>6457</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1607,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1937538</v>
+        <v>6703384</v>
       </c>
       <c r="B10" t="n">
-        <v>75428</v>
+        <v>80477</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,26 +1618,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>229504</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1647,14 +1647,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gäddegöl, nordöst om, Sm</t>
+          <t>Ödetomt, norr om Gräsö mosse, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436083</v>
+        <v>437466</v>
       </c>
       <c r="R10" t="n">
-        <v>6378073</v>
+        <v>6377842</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Ödetomt</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Lönn, vårdträd och högstubbe</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>74965281</v>
+        <v>1937538</v>
       </c>
       <c r="B11" t="n">
-        <v>110077</v>
+        <v>75428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,37 +1734,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>L1 Punkt 320.0 500 m VNV, Sm</t>
+          <t>Gäddegöl, nordöst om, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435808</v>
+        <v>436083</v>
       </c>
       <c r="R11" t="n">
-        <v>6376681</v>
+        <v>6378073</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1788,17 +1797,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1985-01-01</t>
+          <t>2011-04-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6D5h 4625. SOM: Scorzonera humilis. LEG: Lennart Stenberg, Lennart Persson</t>
+          <t>2011-04-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,70 +1816,71 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>200849</v>
+        <v>74965281</v>
       </c>
       <c r="B12" t="n">
-        <v>96705</v>
+        <v>110077</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>535</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brännegölen, norr om, Sm</t>
+          <t>L1 Punkt 320.0 500 m VNV, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434522</v>
+        <v>435808</v>
       </c>
       <c r="R12" t="n">
-        <v>6377835</v>
+        <v>6376681</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1899,12 +1904,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2011-04-05</t>
+          <t>1985-01-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2011-04-05</t>
+          <t>1989-12-31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6D5h 4625. SOM: Scorzonera humilis. LEG: Lennart Stenberg, Lennart Persson</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,33 +1928,32 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Bergbrant vid sumpskog</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Klippa</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>817729</v>
+        <v>200849</v>
       </c>
       <c r="B13" t="n">
-        <v>97733</v>
+        <v>96705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,21 +1961,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>535</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Brid.) E.Britton</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2048,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1276843</v>
+        <v>817729</v>
       </c>
       <c r="B14" t="n">
-        <v>91893</v>
+        <v>97733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,43 +2068,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4660</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Högåsabergen, Sm</t>
+          <t>Brännegölen, norr om, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433902</v>
+        <v>434522</v>
       </c>
       <c r="R14" t="n">
-        <v>6378202</v>
+        <v>6377835</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Bergbrant</t>
+          <t>Bergbrant vid sumpskog</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Asp, grov högstubbe</t>
+          <t>Klippa</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2164,32 +2164,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1849500</v>
+        <v>1276843</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>91893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4660</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2204,17 +2204,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fågelåsen, Sm</t>
+          <t>Högåsabergen, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434561</v>
+        <v>433902</v>
       </c>
       <c r="R15" t="n">
-        <v>6376516</v>
+        <v>6378202</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Asp, grov högstubbe</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2280,37 +2280,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1937533</v>
+        <v>1849500</v>
       </c>
       <c r="B16" t="n">
-        <v>75428</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2320,17 +2320,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Brännegölen, norr om, Sm</t>
+          <t>Fågelåsen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434600</v>
+        <v>434561</v>
       </c>
       <c r="R16" t="n">
-        <v>6377978</v>
+        <v>6376516</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2373,12 +2373,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Bergbrant</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Gran, senvuxen</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2396,56 +2396,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>66535341</v>
+        <v>1937533</v>
       </c>
       <c r="B17" t="n">
-        <v>57141</v>
+        <v>75428</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bondö, Sm</t>
+          <t>Brännegölen, norr om, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437829</v>
+        <v>434600</v>
       </c>
       <c r="R17" t="n">
-        <v>6376541</v>
+        <v>6377978</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2472,22 +2470,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:36</t>
+          <t>2011-04-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:36</t>
+          <t>2011-04-05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,19 +2486,147 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Gran, senvuxen</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>66535341</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bondö, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>437829</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6376541</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vaggeryd</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bondstorp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2017-07-03</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2017-07-03</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 781-2024 artfynd.xlsx
+++ b/artfynd/S 781-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135472902</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135207762</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1849499</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74579220</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1263,6 +1288,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106357869</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1372,6 +1402,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103123401</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1488,6 +1523,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1849514</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1604,6 +1644,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1906155</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1720,6 +1765,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6703384</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1836,6 +1886,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1937538</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1947,6 +2002,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74965281</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2054,6 +2114,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/200849</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2161,6 +2226,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/817729</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2277,6 +2347,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1276843</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2393,6 +2468,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1849500</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2509,6 +2589,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1937533</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2627,8 +2712,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66535341</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 781-2024 artfynd.xlsx
+++ b/artfynd/S 781-2024 artfynd.xlsx
@@ -918,7 +918,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Boberg, Håkan  Åberg</t>
+          <t>Håkan  Åberg, Hans Boberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/S 781-2024 artfynd.xlsx
+++ b/artfynd/S 781-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135472902</v>
       </c>
       <c r="B2" t="n">
-        <v>58061</v>
+        <v>58066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135207762</v>
       </c>
       <c r="B3" t="n">
-        <v>99112</v>
+        <v>99162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,23 +812,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>223597</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
@@ -918,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan  Åberg, Hans Boberg</t>
+          <t>Hans Boberg, Håkan  Åberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/S 781-2024 artfynd.xlsx
+++ b/artfynd/S 781-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135207762</v>
       </c>
       <c r="B3" t="n">
-        <v>99162</v>
+        <v>99189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 781-2024 artfynd.xlsx
+++ b/artfynd/S 781-2024 artfynd.xlsx
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Boberg, Håkan  Åberg</t>
+          <t>Håkan  Åberg, Hans Boberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/S 781-2024 artfynd.xlsx
+++ b/artfynd/S 781-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,57 +680,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1849499</v>
+        <v>135472902</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>58066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>102626</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1K</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högåsabergen, bäck norr om, Sm</t>
+          <t>Tranflyet, Tranflyet, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433755</v>
+        <v>437072</v>
       </c>
       <c r="R2" t="n">
-        <v>6378877</v>
+        <v>6379592</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-04-05</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-04-05</t>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>19:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,41 +780,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Blandsumpskog vid bäck</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Björk, gran</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Bob Lind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Bob Lind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1849499</t>
+          <t>https://artportalen.se/Sighting/135472902</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74579220</v>
+        <v>135207762</v>
       </c>
       <c r="B3" t="n">
-        <v>99140</v>
+        <v>99194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +812,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>223597</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>L28 Högåsabergen nord, Sm</t>
+          <t>Högåsabergen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433982</v>
+        <v>433704</v>
       </c>
       <c r="R3" t="n">
-        <v>6378958</v>
+        <v>6379461</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,17 +878,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1987-12-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6D6h 1907. SOM: Listera cordata. LEG: Lennart Stenberg, Lennart Persson</t>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,92 +902,81 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Sluttande skog i vitmossa</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Boberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Hans Boberg, Håkan  Åberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74579220</t>
+          <t>https://artportalen.se/Sighting/135207762</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106357869</v>
+        <v>1849499</v>
       </c>
       <c r="B4" t="n">
-        <v>57864</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100011</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bongebo skogsbilväg b, Sm</t>
+          <t>Högåsabergen, bäck norr om, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438337</v>
+        <v>433755</v>
       </c>
       <c r="R4" t="n">
-        <v>6378990</v>
+        <v>6378877</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,27 +1000,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2011-04-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flög fram och tillbala bland trädtopparna. Ungfågel.</t>
+          <t>2011-04-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,31 +1016,41 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Blandsumpskog vid bäck</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Björk, gran</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marcus Svensson</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marcus Svensson</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106357869</t>
+          <t>https://artportalen.se/Sighting/1849499</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103123401</v>
+        <v>74579220</v>
       </c>
       <c r="B5" t="n">
-        <v>57141</v>
+        <v>99140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1057,46 +1058,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bongebo skogsbilväg a, Sm</t>
+          <t>L28 Högåsabergen nord, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438605</v>
+        <v>433982</v>
       </c>
       <c r="R5" t="n">
-        <v>6378918</v>
+        <v>6378958</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1123,12 +1112,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>1987-12-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6D6h 1907. SOM: Listera cordata. LEG: Lennart Stenberg, Lennart Persson</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,53 +1133,62 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Sluttande skog i vitmossa</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marcus Svensson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marcus Svensson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103123401</t>
+          <t>https://artportalen.se/Sighting/74579220</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1849514</v>
+        <v>106357869</v>
       </c>
       <c r="B6" t="n">
-        <v>79327</v>
+        <v>57864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100011</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1193,24 +1196,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svansjön, sydväst om, Sm</t>
+          <t>Bongebo skogsbilväg b, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435286</v>
+        <v>438337</v>
       </c>
       <c r="R6" t="n">
-        <v>6378953</v>
+        <v>6378990</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,12 +1240,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2011-04-20</t>
+          <t>2023-01-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2011-04-20</t>
+          <t>2023-01-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flög fram och tillbala bland trädtopparna. Ungfågel.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,41 +1271,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Marcus Svensson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Marcus Svensson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1849514</t>
+          <t>https://artportalen.se/Sighting/106357869</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1906155</v>
+        <v>103123401</v>
       </c>
       <c r="B7" t="n">
-        <v>80367</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,21 +1303,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6457</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1314,24 +1325,27 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ödetomt, norr om Gräsö mosse, Sm</t>
+          <t>Bongebo skogsbilväg a, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437466</v>
+        <v>438605</v>
       </c>
       <c r="R7" t="n">
-        <v>6377842</v>
+        <v>6378918</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1355,12 +1369,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2011-04-20</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2011-04-20</t>
+          <t>2022-08-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,68 +1385,58 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Ödetomt</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Lönn, vårdträd och högstubbe</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Marcus Svensson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Marcus Svensson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1906155</t>
+          <t>https://artportalen.se/Sighting/103123401</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6703384</v>
+        <v>1849514</v>
       </c>
       <c r="B8" t="n">
-        <v>80477</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229504</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1442,14 +1446,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ödetomt, norr om Gräsö mosse, Sm</t>
+          <t>Svansjön, sydväst om, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437466</v>
+        <v>435286</v>
       </c>
       <c r="R8" t="n">
-        <v>6377842</v>
+        <v>6378953</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1495,12 +1499,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Ödetomt</t>
+          <t>Tallmosse</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Lönn, vårdträd och högstubbe</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1517,43 +1521,43 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6703384</t>
+          <t>https://artportalen.se/Sighting/1849514</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1937538</v>
+        <v>1906155</v>
       </c>
       <c r="B9" t="n">
-        <v>75428</v>
+        <v>80367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>6457</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1563,14 +1567,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gäddegöl, nordöst om, Sm</t>
+          <t>Ödetomt, norr om Gräsö mosse, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436083</v>
+        <v>437466</v>
       </c>
       <c r="R9" t="n">
-        <v>6378073</v>
+        <v>6377842</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,12 +1620,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Blandsumpskog</t>
+          <t>Ödetomt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Lönn, vårdträd och högstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1638,16 +1642,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1937538</t>
+          <t>https://artportalen.se/Sighting/1906155</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>74965281</v>
+        <v>6703384</v>
       </c>
       <c r="B10" t="n">
-        <v>110077</v>
+        <v>80477</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,37 +1659,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>229504</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>L1 Punkt 320.0 500 m VNV, Sm</t>
+          <t>Ödetomt, norr om Gräsö mosse, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435808</v>
+        <v>437466</v>
       </c>
       <c r="R10" t="n">
-        <v>6376681</v>
+        <v>6377842</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1709,17 +1722,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1985-01-01</t>
+          <t>2011-04-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6D5h 4625. SOM: Scorzonera humilis. LEG: Lennart Stenberg, Lennart Persson</t>
+          <t>2011-04-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,72 +1741,82 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Ödetomt</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Lönn, vårdträd och högstubbe</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74965281</t>
+          <t>https://artportalen.se/Sighting/6703384</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>200849</v>
+        <v>1937538</v>
       </c>
       <c r="B11" t="n">
-        <v>96705</v>
+        <v>75428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>535</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brännegölen, norr om, Sm</t>
+          <t>Gäddegöl, nordöst om, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434522</v>
+        <v>436083</v>
       </c>
       <c r="R11" t="n">
-        <v>6377835</v>
+        <v>6378073</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,12 +1843,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2011-04-05</t>
+          <t>2011-04-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2011-04-05</t>
+          <t>2011-04-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,12 +1862,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Bergbrant vid sumpskog</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Klippa</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1866,54 +1884,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/200849</t>
+          <t>https://artportalen.se/Sighting/1937538</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>817729</v>
+        <v>74965281</v>
       </c>
       <c r="B12" t="n">
-        <v>97733</v>
+        <v>110077</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brännegölen, norr om, Sm</t>
+          <t>L1 Punkt 320.0 500 m VNV, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434522</v>
+        <v>435808</v>
       </c>
       <c r="R12" t="n">
-        <v>6377835</v>
+        <v>6376681</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1937,12 +1955,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2011-04-05</t>
+          <t>1985-01-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2011-04-05</t>
+          <t>1989-12-31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6D5h 4625. SOM: Scorzonera humilis. LEG: Lennart Stenberg, Lennart Persson</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,38 +1979,37 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Bergbrant vid sumpskog</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Klippa</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Örjan Fritz</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/817729</t>
+          <t>https://artportalen.se/Sighting/74965281</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1276843</v>
+        <v>200849</v>
       </c>
       <c r="B13" t="n">
-        <v>91893</v>
+        <v>96705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,43 +2017,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4660</v>
+        <v>535</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brid.) E.Britton</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Högåsabergen, Sm</t>
+          <t>Brännegölen, norr om, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433902</v>
+        <v>434522</v>
       </c>
       <c r="R13" t="n">
-        <v>6378202</v>
+        <v>6377835</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2077,12 +2090,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Bergbrant</t>
+          <t>Bergbrant vid sumpskog</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Asp, grov högstubbe</t>
+          <t>Klippa</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2099,63 +2112,54 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1276843</t>
+          <t>https://artportalen.se/Sighting/200849</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1849500</v>
+        <v>817729</v>
       </c>
       <c r="B14" t="n">
-        <v>79327</v>
+        <v>97733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fågelåsen, Sm</t>
+          <t>Brännegölen, norr om, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434561</v>
+        <v>434522</v>
       </c>
       <c r="R14" t="n">
-        <v>6376516</v>
+        <v>6377835</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2198,12 +2202,12 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Bergbrant</t>
+          <t>Bergbrant vid sumpskog</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Klippa</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2220,43 +2224,43 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1849500</t>
+          <t>https://artportalen.se/Sighting/817729</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1937533</v>
+        <v>1276843</v>
       </c>
       <c r="B15" t="n">
-        <v>75428</v>
+        <v>91893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>4660</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2266,14 +2270,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Brännegölen, norr om, Sm</t>
+          <t>Högåsabergen, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434600</v>
+        <v>433902</v>
       </c>
       <c r="R15" t="n">
-        <v>6377978</v>
+        <v>6378202</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2319,12 +2323,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Bergbrant</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Gran, senvuxen</t>
+          <t>Asp, grov högstubbe</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2341,38 +2345,38 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1937533</t>
+          <t>https://artportalen.se/Sighting/1276843</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>66535341</v>
+        <v>1849500</v>
       </c>
       <c r="B16" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2380,26 +2384,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bondö, Sm</t>
+          <t>Fågelåsen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437829</v>
+        <v>434561</v>
       </c>
       <c r="R16" t="n">
-        <v>6376541</v>
+        <v>6376516</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2423,22 +2425,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:36</t>
+          <t>2011-04-05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:36</t>
+          <t>2011-04-05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2449,20 +2441,274 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Bergbrant</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Örjan Fritz</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1849500</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1937533</v>
+      </c>
+      <c r="B17" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Brännegölen, norr om, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>434600</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6377978</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vaggeryd</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bondstorp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2011-04-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2011-04-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Gran, senvuxen</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Örjan Fritz</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1937533</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>66535341</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bondö, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>437829</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6376541</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vaggeryd</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bondstorp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2017-07-03</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2017-07-03</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/66535341</t>
         </is>
@@ -2485,6 +2731,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 781-2024 artfynd.xlsx
+++ b/artfynd/S 781-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135207762</v>
       </c>
       <c r="B3" t="n">
-        <v>99194</v>
+        <v>99196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 781-2024 artfynd.xlsx
+++ b/artfynd/S 781-2024 artfynd.xlsx
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan  Åberg, Hans Boberg</t>
+          <t>Hans Boberg, Håkan  Åberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/S 781-2024 artfynd.xlsx
+++ b/artfynd/S 781-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135472902</v>
       </c>
       <c r="B2" t="n">
-        <v>58066</v>
+        <v>58068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135207762</v>
       </c>
       <c r="B3" t="n">
-        <v>99196</v>
+        <v>99213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 781-2024 artfynd.xlsx
+++ b/artfynd/S 781-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135207762</v>
       </c>
       <c r="B3" t="n">
-        <v>99213</v>
+        <v>99214</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 781-2024 artfynd.xlsx
+++ b/artfynd/S 781-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135207762</v>
       </c>
       <c r="B3" t="n">
-        <v>99214</v>
+        <v>99215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 781-2024 artfynd.xlsx
+++ b/artfynd/S 781-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>135207762</v>
       </c>
       <c r="B3" t="n">
-        <v>99215</v>
+        <v>99216</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Boberg, Håkan  Åberg</t>
+          <t>Håkan  Åberg, Hans Boberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
